--- a/results/job_matches_2026-08-26.xlsx
+++ b/results/job_matches_2026-08-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,25 +888,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>AWS Python Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=493f15e83d88a6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=834d52dff47fe0c1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Python Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Peoples Gas System</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834d52dff47fe0c1</t>
+          <t>https://www.indeed.com/viewjob?jk=d32754dc82fcb92a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Systems Engineer, Data Management</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Peoples Gas System</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32754dc82fcb92a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed5484e209306fd8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, Data Management</t>
+          <t>Senior Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>AAA Auto Club Enterprises</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed5484e209306fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e80b460b21ce73</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer</t>
+          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AAA Auto Club Enterprises</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e80b460b21ce73</t>
+          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
         </is>
       </c>
     </row>
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>OneDome</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, BigQuery</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
+          <t>https://www.indeed.com/viewjob?jk=16e7886502273f96</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Backend Java Developer | Jersey City, US</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OneDome</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, BigQuery</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e7886502273f96</t>
+          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Backend Java Developer | Jersey City, US</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
+          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Data Engineering Summer Intern (May-Aug '27)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3f0b99fc7578c909</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineering Summer Intern (May-Aug '27)</t>
+          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f0b99fc7578c909</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4bc1c52db1db4e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4bc1c52db1db4e</t>
+          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
+          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>BI / Data Architect (Remote)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
+          <t>https://www.indeed.com/viewjob?jk=64614fd6a49cf213</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BI / Data Architect (Remote)</t>
+          <t>Campus - Technology Program Intern</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,69 +1431,69 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64614fd6a49cf213</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Campus - Technology Program Intern</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Windsor Mill, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
+          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Inadev Corporation</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2784516465b56a61</t>
+          <t>https://www.indeed.com/viewjob?jk=cc8011b3d20c58b9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Inadev Corporation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
+          <t>https://www.indeed.com/viewjob?jk=2784516465b56a61</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
+          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
         </is>
       </c>
     </row>
@@ -1593,47 +1593,47 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
+          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wrench.ai Inc</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, PostgreSQL, ELT</t>
+          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83be4ed684048bae</t>
+          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
         </is>
       </c>
     </row>
@@ -1693,25 +1693,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Java Engineer | Jersey City, US</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
+          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 2</t>
+          <t>Java Engineer | Plano/Columbus, US</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
+          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Sr. Platform Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>Wrench.ai Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, PostgreSQL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=83be4ed684048bae</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ab440c93bda25b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps &amp; Platform Engineer - Remote Role</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
+          <t>https://www.indeed.com/viewjob?jk=abf2c8858d372138</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Whiteland, IN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
+          <t>https://www.indeed.com/viewjob?jk=08a226425e0c1a0f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
+          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cards Java Developer</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5208fb6417aa24f6</t>
+          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Praia Health</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
+          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Java Backend &amp; AI Engineer – Wealth Management</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EL SHADDAI TECHNOLOGIES</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, MLflow, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a59b3cdfe58cc35</t>
+          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>Integration &amp; API Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
+          <t>https://www.indeed.com/viewjob?jk=96fb1a89b2f01b9f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Business Intelligence Developer</t>
+          <t>DevOps &amp; Platform Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Gopher Resource, LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer with Azure Databricks</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Aurum Groups</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Whiteland, IN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
+          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cards Java Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
+          <t>https://www.indeed.com/viewjob?jk=5208fb6417aa24f6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer GCP Vertex AI Apache Iceberg</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Cloud Storage, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4819706c3ee3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
+          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SQL Database Engineer</t>
+          <t>Data Platform &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BMR infotek</t>
+          <t>Gopher Resource, LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Data Engineer with Azure Databricks</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Aurum Groups</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Praia Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Machine Learning Engineer GCP Vertex AI Apache Iceberg</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>GCP, BigQuery, Cloud Storage, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4819706c3ee3c8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
+          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
+          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>SQL Database Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>BMR infotek</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Epik Solutions</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
+          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
+          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
+          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Solutions developer</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Engineering and Automation , Aerospace &amp; Defense</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
+          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Platform Engineer (175364)</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
+          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TheGuarantors</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4e67065f473c15</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Data Solutions developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Engineering and Automation , Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
+          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer II - ML and Observability</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack Innovations</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
+          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Data &amp; AI Platform</t>
+          <t>Platform Engineer (175364)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SimplePractice</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b00d7042d542536</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer, Associate - NASA</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>INNOVIM, LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, CI/CD, Docker, Kubernetes, Bitbucket</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,67 +3366,67 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77d0865eb1cf492</t>
+          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>TheGuarantors</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Controller Transformation Analyst</t>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
+          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>INFINITY HOME SERVICES</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - ML and Observability</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jean Martin</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+          <t>DevOps Engineer, Data &amp; AI Platform</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+          <t>https://www.indeed.com/viewjob?jk=9b00d7042d542536</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
+          <t>Software Engineer, Associate - NASA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, CI/CD, Docker, Kubernetes, Bitbucket</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
+          <t>https://www.indeed.com/viewjob?jk=c77d0865eb1cf492</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18271f0af24fff11</t>
+          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Controller Transformation Analyst</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Accelerate Learning Inc.</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ddf4a6188d3a180</t>
+          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Engineer III, Business Intelligence</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>INFINITY HOME SERVICES</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,15 +3741,295 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Jean Martin</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Java Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Software Developer Senior</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>City of Charlotte, NC</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8009ac0fbc46342</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18271f0af24fff11</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Software Architect</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Accelerate Learning Inc.</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ddf4a6188d3a180</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Engineer III, Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Mobis Parts America, LLC.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Fountain Valley, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3b3103a10d60cdc6</t>
         </is>

--- a/results/job_matches_2026-08-26.xlsx
+++ b/results/job_matches_2026-08-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BI / Data Architect (Remote)</t>
+          <t>Campus - Technology Program Intern</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,69 +1396,69 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64614fd6a49cf213</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Campus - Technology Program Intern</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Windsor Mill, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
+          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Index Analytics LLC</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Windsor Mill, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
+          <t>https://www.indeed.com/viewjob?jk=cc8011b3d20c58b9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Inadev Corporation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8011b3d20c58b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2784516465b56a61</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Inadev Corporation</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2784516465b56a61</t>
+          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
         </is>
       </c>
     </row>
@@ -1588,25 +1588,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
+          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>CDK Global</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Java Engineer | Jersey City, US</t>
+          <t>Senior Data Engineer — Translational Data Products</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
+          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Java Engineer | Plano/Columbus, US</t>
+          <t>Java Engineer | Jersey City, US</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer</t>
+          <t>Java Engineer | Plano/Columbus, US</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wrench.ai Inc</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, PostgreSQL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83be4ed684048bae</t>
+          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
+          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Evolve vacation rentals</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ab440c93bda25b</t>
+          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Senior Software Engineer (Revenue)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Zuora</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf2c8858d372138</t>
+          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08a226425e0c1a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ab440c93bda25b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 2</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
+          <t>https://www.indeed.com/viewjob?jk=abf2c8858d372138</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=08a226425e0c1a0f</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
+          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Integration &amp; API Architect</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fb1a89b2f01b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps &amp; Platform Engineer - Remote Role</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
+          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Whiteland, IN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
+          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cards Java Developer</t>
+          <t>Integration &amp; API Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5208fb6417aa24f6</t>
+          <t>https://www.indeed.com/viewjob?jk=96fb1a89b2f01b9f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>DevOps &amp; Platform Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
+          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Business Intelligence Developer</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gopher Resource, LLC</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
+          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer with Azure Databricks</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Aurum Groups</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Whiteland, IN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
+          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Praia Health</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
+          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Sr. Data Engineer with Azure Databricks</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Aurum Groups</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
+          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer GCP Vertex AI Apache Iceberg</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Praia Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Cloud Storage, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4819706c3ee3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
+          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Platform &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Gopher Resource, LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SQL Database Engineer</t>
+          <t>Machine Learning Engineer GCP Vertex AI Apache Iceberg</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BMR infotek</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>GCP, BigQuery, Cloud Storage, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4819706c3ee3c8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Epik Solutions</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
+          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>SQL Database Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>BMR infotek</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Epik Solutions</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
+          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
+          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
+          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer - DBT &amp; Redshift</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Azure, Medallion Architecture, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
+          <t>https://www.indeed.com/viewjob?jk=35214e13f0757c04</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,102 +3051,102 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
+          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
+          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Solutions developer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Engineering and Automation , Aerospace &amp; Defense</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Platform Engineer (175364)</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Data Solutions developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Engineering and Automation , Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TheGuarantors</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+          <t>Platform Engineer (175364)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
+          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer II - ML and Observability</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TheGuarantors</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
+          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Data &amp; AI Platform</t>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SimplePractice</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b00d7042d542536</t>
+          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer, Associate - NASA</t>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>INNOVIM, LLC</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, CI/CD, Docker, Kubernetes, Bitbucket</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,67 +3611,67 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77d0865eb1cf492</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Developer / Data Solutions Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Controller Transformation Analyst</t>
+          <t>Software Engineer II - ML and Observability</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
+          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer, Associate - NASA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>INFINITY HOME SERVICES</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, CI/CD, Docker, Kubernetes, Bitbucket</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
+          <t>https://www.indeed.com/viewjob?jk=c77d0865eb1cf492</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer, Data &amp; AI Platform</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Jean Martin</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+          <t>https://www.indeed.com/viewjob?jk=9b00d7042d542536</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Controller Transformation Analyst</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
+          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Developer Senior</t>
+          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>City of Charlotte, NC</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8009ac0fbc46342</t>
+          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>INFINITY HOME SERVICES</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
+          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Jean Martin</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18271f0af24fff11</t>
+          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Accelerate Learning Inc.</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ddf4a6188d3a180</t>
+          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Engineer III, Business Intelligence</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,77 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b3103a10d60cdc6</t>
+          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Software Developer Senior</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>City of Charlotte, NC</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8009ac0fbc46342</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-26.xlsx
+++ b/results/job_matches_2026-08-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineering Summer Intern (May-Aug '27)</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f0b99fc7578c909</t>
+          <t>https://www.indeed.com/viewjob?jk=edcca601c37b3df4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4bc1c52db1db4e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c6800ab3996b5b3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineering Summer Intern (May-Aug '27)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
+          <t>https://www.indeed.com/viewjob?jk=3f0b99fc7578c909</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4bc1c52db1db4e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
+          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Campus - Technology Program Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
+          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Index Analytics LLC</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Windsor Mill, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Windsor Mill, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8011b3d20c58b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Inadev Corporation</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2784516465b56a61</t>
+          <t>https://www.indeed.com/viewjob?jk=cc8011b3d20c58b9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
+          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
+          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Java Engineer | Jersey City, US</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
+          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Java Engineer | Plano/Columbus, US</t>
+          <t>Java Engineer | Jersey City, US</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Java Engineer | Plano/Columbus, US</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps &amp; Platform Engineer - Remote Role</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
+          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
+          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Whiteland, IN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
+          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Platform &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Gopher Resource, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Whiteland, IN, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
+          <t>DevOps &amp; Platform Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer with Azure Databricks</t>
+          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Aurum Groups</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
+          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Sr. Data Engineer with Azure Databricks</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Praia Health</t>
+          <t>Aurum Groups</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
+          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Praia Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Business Intelligence Developer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Gopher Resource, LLC</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
+          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Epik Solutions</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Epik Solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
+          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,19 +2946,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
+          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - DBT &amp; Redshift</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Medallion Architecture, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35214e13f0757c04</t>
+          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Data Engineer - DBT &amp; Redshift</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>Redshift, RDS, Azure, Medallion Architecture, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
+          <t>https://www.indeed.com/viewjob?jk=35214e13f0757c04</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,24 +3076,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,42 +3146,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
+          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
+          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Solutions developer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Engineering and Automation , Aerospace &amp; Defense</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Data Solutions developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Engineering and Automation , Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Platform Engineer (175364)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
+          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Platform Engineer (175364)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,19 +3506,19 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TheGuarantors</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
+          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>TheGuarantors</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
+          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Developer / Data Solutions Developer</t>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer II - ML and Observability</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
+          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Software Developer / Data Solutions Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer, Associate - NASA</t>
+          <t>Software Engineer II - ML and Observability</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>INNOVIM, LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, CI/CD, Docker, Kubernetes, Bitbucket</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77d0865eb1cf492</t>
+          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
         </is>
       </c>
     </row>
@@ -3793,52 +3793,52 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineer, Associate - NASA</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, CI/CD, Docker, Kubernetes, Bitbucket</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c77d0865eb1cf492</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Controller Transformation Analyst</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
+          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
+          <t>Controller Transformation Analyst</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>INFINITY HOME SERVICES</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
+          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Jean Martin</t>
+          <t>INFINITY HOME SERVICES</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Jean Martin</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
+          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Developer Senior</t>
+          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>City of Charlotte, NC</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,15 +4091,85 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AI Agentic Software Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Software Developer Senior</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>City of Charlotte, NC</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a8009ac0fbc46342</t>
         </is>

--- a/results/job_matches_2026-08-26.xlsx
+++ b/results/job_matches_2026-08-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ziply Fiber</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.2</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6405304b5156b40</t>
+          <t>https://www.indeed.com/viewjob?jk=451eef560601ded5</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=451eef560601ded5</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3ee7b1db2cccd5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3ee7b1db2cccd5</t>
+          <t>https://www.indeed.com/viewjob?jk=20d1d5763df13b0f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20d1d5763df13b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=03deb24662c2d57b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03deb24662c2d57b</t>
+          <t>https://www.indeed.com/viewjob?jk=f191710314c15359</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f191710314c15359</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d939da0bcff1af</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d939da0bcff1af</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e2c8f86b9525b8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e2c8f86b9525b8</t>
+          <t>https://www.indeed.com/viewjob?jk=082b971e34568c1f</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Vista, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=082b971e34568c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=26d52f1deebd9cc0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Sr Talend Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vista, CA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d52f1deebd9cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=743665ae918f4a0c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Talend Data Engineer</t>
+          <t>Senior Data Engineer (Analytics)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743665ae918f4a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=181a31f219accf44</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Analytics)</t>
+          <t>AWS Python Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=181a31f219accf44</t>
+          <t>https://www.indeed.com/viewjob?jk=834d52dff47fe0c1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS Python Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Peoples Gas System</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834d52dff47fe0c1</t>
+          <t>https://www.indeed.com/viewjob?jk=d32754dc82fcb92a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Systems Engineer, Data Management</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Peoples Gas System</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32754dc82fcb92a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed5484e209306fd8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, Data Management</t>
+          <t>Senior Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>AAA Auto Club Enterprises</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed5484e209306fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e80b460b21ce73</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer</t>
+          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AAA Auto Club Enterprises</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e80b460b21ce73</t>
+          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>OneDome</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, BigQuery</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
+          <t>https://www.indeed.com/viewjob?jk=16e7886502273f96</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Backend Java Developer | Jersey City, US</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OneDome</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, BigQuery</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e7886502273f96</t>
+          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Backend Java Developer | Jersey City, US</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
+          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=edcca601c37b3df4</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edcca601c37b3df4</t>
+          <t>https://www.indeed.com/viewjob?jk=1c6800ab3996b5b3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Engineering Summer Intern (May-Aug '27)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c6800ab3996b5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f0b99fc7578c909</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineering Summer Intern (May-Aug '27)</t>
+          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f0b99fc7578c909</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4bc1c52db1db4e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4bc1c52db1db4e</t>
+          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,104 +1361,104 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
+          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Windsor Mill, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
+          <t>https://www.indeed.com/viewjob?jk=cc8011b3d20c58b9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Index Analytics LLC</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Windsor Mill, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
+          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8011b3d20c58b9</t>
+          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,59 +1546,59 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
+          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>CDK Global</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
+          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer — Translational Data Products</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CDK Global</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — Translational Data Products</t>
+          <t>Java Engineer | Jersey City, US</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Java Engineer | Plano/Columbus, US</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Java Engineer | Jersey City, US</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Evolve vacation rentals</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
+          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Java Engineer | Plano/Columbus, US</t>
+          <t>Senior Software Engineer (Revenue)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Zuora</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Evolve vacation rentals</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
+          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Revenue)</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Zuora</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ab440c93bda25b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
+          <t>https://www.indeed.com/viewjob?jk=abf2c8858d372138</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ab440c93bda25b</t>
+          <t>https://www.indeed.com/viewjob?jk=08a226425e0c1a0f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf2c8858d372138</t>
+          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08a226425e0c1a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
+          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
+          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Integration &amp; API Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=96fb1a89b2f01b9f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
+          <t>https://www.indeed.com/viewjob?jk=2b83410cfb11a99d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Integration &amp; API Architect</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fb1a89b2f01b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
+          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Whiteland, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
+          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Platform &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Gopher Resource, LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Whiteland, IN, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Business Intelligence Developer</t>
+          <t>DevOps &amp; Platform Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gopher Resource, LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps &amp; Platform Engineer - Remote Role</t>
+          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
+          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
+          <t>Sr. Data Engineer with Azure Databricks</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Aurum Groups</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
+          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer with Azure Databricks</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Aurum Groups</t>
+          <t>Praia Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
+          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Praia Health</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
+          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Machine Learning Engineer GCP Vertex AI Apache Iceberg</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>GCP, BigQuery, Cloud Storage, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4819706c3ee3c8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer GCP Vertex AI Apache Iceberg</t>
+          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Cloud Storage, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4819706c3ee3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
+          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>SQL Database Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>BMR infotek</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SQL Database Engineer</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BMR infotek</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Epik Solutions</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
+          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Epik Solutions</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,19 +2946,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
+          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
+          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - DBT &amp; Redshift</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>Redshift, RDS, Azure, Medallion Architecture, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
+          <t>https://www.indeed.com/viewjob?jk=35214e13f0757c04</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - DBT &amp; Redshift</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Medallion Architecture, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35214e13f0757c04</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,24 +3076,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
+          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,42 +3146,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
+          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Data Solutions developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Engineering and Automation , Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
+          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Solutions developer</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Engineering and Automation , Aerospace &amp; Defense</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Platform Engineer (175364)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Platform Engineer (175364)</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,19 +3506,19 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
+          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TheGuarantors</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TheGuarantors</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
+          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
+          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Software Developer / Data Solutions Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Developer / Data Solutions Developer</t>
+          <t>Software Engineer II - ML and Observability</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer II - ML and Observability</t>
+          <t>DevOps Engineer, Data &amp; AI Platform</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
+          <t>https://www.indeed.com/viewjob?jk=9b00d7042d542536</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Data &amp; AI Platform</t>
+          <t>Software Engineer, Associate - NASA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SimplePractice</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, CI/CD, Docker, Kubernetes, Bitbucket</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,59 +3786,59 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b00d7042d542536</t>
+          <t>https://www.indeed.com/viewjob?jk=c77d0865eb1cf492</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer, Associate - NASA</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>INNOVIM, LLC</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, CI/CD, Docker, Kubernetes, Bitbucket</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77d0865eb1cf492</t>
+          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Controller Transformation Analyst</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Controller Transformation Analyst</t>
+          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
+          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>INFINITY HOME SERVICES</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
+          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>INFINITY HOME SERVICES</t>
+          <t>Jean Martin</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Jean Martin</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
+          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
+          <t>AI Agentic Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
+          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AI Agentic Software Engineer</t>
+          <t>Software Developer Senior</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>City of Charlotte, NC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4135,41 +4135,6 @@
         </is>
       </c>
       <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Software Developer Senior</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>City of Charlotte, NC</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a8009ac0fbc46342</t>
         </is>

--- a/results/job_matches_2026-08-26.xlsx
+++ b/results/job_matches_2026-08-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,25 +1098,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Backend Java Developer | Jersey City, US</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
+          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=edcca601c37b3df4</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edcca601c37b3df4</t>
+          <t>https://www.indeed.com/viewjob?jk=1c6800ab3996b5b3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Engineering Summer Intern (May-Aug '27)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c6800ab3996b5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f0b99fc7578c909</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineering Summer Intern (May-Aug '27)</t>
+          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f0b99fc7578c909</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4bc1c52db1db4e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4bc1c52db1db4e</t>
+          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,69 +1326,69 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
+          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Windsor Mill, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Index Analytics LLC</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Windsor Mill, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0e151be0bbb235</t>
         </is>
       </c>
     </row>
@@ -3723,17 +3723,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Data &amp; AI Platform</t>
+          <t>Software Engineer, Associate - NASA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SimplePractice</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, CI/CD, Docker, Kubernetes, Bitbucket</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b00d7042d542536</t>
+          <t>https://www.indeed.com/viewjob?jk=c77d0865eb1cf492</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer, Associate - NASA</t>
+          <t>Controller Transformation Analyst</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>INNOVIM, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, CI/CD, Docker, Kubernetes, Bitbucket</t>
+          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77d0865eb1cf492</t>
+          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Controller Transformation Analyst</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>INFINITY HOME SERVICES</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
+          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
+          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Jean Martin</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>INFINITY HOME SERVICES</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
+          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Jean Martin</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>AI Agentic Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
+          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
+          <t>Software Developer Senior</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>City of Charlotte, NC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4065,76 +4065,6 @@
         </is>
       </c>
       <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>AI Agentic Software Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Siemens</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Software Developer Senior</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>City of Charlotte, NC</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a8009ac0fbc46342</t>
         </is>

--- a/results/job_matches_2026-08-26.xlsx
+++ b/results/job_matches_2026-08-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AAA Auto Club Enterprises</t>
+          <t>Premier Nutrition Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e80b460b21ce73</t>
+          <t>https://www.indeed.com/viewjob?jk=7bf2e42812735206</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+          <t>Senior Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>AAA Auto Club Enterprises</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e80b460b21ce73</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
+          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OneDome</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,77 +1081,77 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, BigQuery</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e7886502273f96</t>
+          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>OneDome</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, BigQuery</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=16e7886502273f96</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edcca601c37b3df4</t>
+          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c6800ab3996b5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=edcca601c37b3df4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineering Summer Intern (May-Aug '27)</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f0b99fc7578c909</t>
+          <t>https://www.indeed.com/viewjob?jk=1c6800ab3996b5b3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
+          <t>Data Engineering Summer Intern (May-Aug '27)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4bc1c52db1db4e</t>
+          <t>https://www.indeed.com/viewjob?jk=3f0b99fc7578c909</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4bc1c52db1db4e</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,69 +1326,69 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Index Analytics LLC</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Windsor Mill, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
+          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Windsor Mill, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0e151be0bbb235</t>
+          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8011b3d20c58b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0e151be0bbb235</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
+          <t>https://www.indeed.com/viewjob?jk=cc8011b3d20c58b9</t>
         </is>
       </c>
     </row>
@@ -1518,25 +1518,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
+          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
+          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CDK Global</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — Translational Data Products</t>
+          <t>Technical Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, ETL</t>
+          <t>AWS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7d8caa90f5aba1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>CDK Global</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Java Engineer | Jersey City, US</t>
+          <t>Senior Associate - Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
+          <t>https://www.indeed.com/viewjob?jk=3282af658369b2af</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Java Engineer | Plano/Columbus, US</t>
+          <t>Senior Data Engineer — Translational Data Products</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Engineer | Jersey City, US</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Evolve vacation rentals</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Revenue)</t>
+          <t>Java Engineer | Plano/Columbus, US</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Zuora</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
+          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
+          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Evolve vacation rentals</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ab440c93bda25b</t>
+          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Senior Software Engineer (Revenue)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Zuora</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,19 +1931,19 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf2c8858d372138</t>
+          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08a226425e0c1a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ab440c93bda25b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
+          <t>https://www.indeed.com/viewjob?jk=abf2c8858d372138</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 2</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
+          <t>https://www.indeed.com/viewjob?jk=08a226425e0c1a0f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
+          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Integration &amp; API Architect</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fb1a89b2f01b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b83410cfb11a99d</t>
+          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>Integration &amp; API Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
+          <t>https://www.indeed.com/viewjob?jk=96fb1a89b2f01b9f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Benda Infotech</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Whiteland, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a7e25c97039733</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Business Intelligence Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gopher Resource, LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
+          <t>https://www.indeed.com/viewjob?jk=2b83410cfb11a99d</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
+          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer with Azure Databricks</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Aurum Groups</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
+          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Praia Health</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Whiteland, IN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
+          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer GCP Vertex AI Apache Iceberg</t>
+          <t>Sr. Data Engineer with Azure Databricks</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Aurum Groups</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Cloud Storage, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4819706c3ee3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Praia Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2617,11 +2617,11 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
+          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
+          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SQL Database Engineer</t>
+          <t>Data Platform &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BMR infotek</t>
+          <t>Gopher Resource, LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
+          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
+          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Epik Solutions</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
+          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>SQL Database Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>BMR infotek</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Epik Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
+          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
+          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - DBT &amp; Redshift</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Medallion Architecture, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35214e13f0757c04</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
+          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
+          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer (Data Architecture)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,42 +3146,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
+          <t>https://www.indeed.com/viewjob?jk=46aed55033a852ae</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,102 +3191,102 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
+          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
+          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Solutions developer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Engineering and Automation , Aerospace &amp; Defense</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Platform Engineer (175364)</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Data Solutions developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Engineering and Automation , Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TheGuarantors</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+          <t>Platform Engineer (175364)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
+          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Developer / Data Solutions Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>TheGuarantors</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer II - ML and Observability</t>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
+          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer, Associate - NASA</t>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>INNOVIM, LLC</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, CI/CD, Docker, Kubernetes, Bitbucket</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77d0865eb1cf492</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Controller Transformation Analyst</t>
+          <t>Software Developer / Data Solutions Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
+          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
+          <t>Software Engineer II - ML and Observability</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
+          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>INFINITY HOME SERVICES</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Controller Transformation Analyst</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Jean Martin</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,19 +3926,19 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>INFINITY HOME SERVICES</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
+          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Jean Martin</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
+          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI Agentic Software Engineer</t>
+          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
+          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Developer Senior</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>City of Charlotte, NC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,15 +4056,120 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AI Agentic Software Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Software Developer Senior</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>City of Charlotte, NC</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a8009ac0fbc46342</t>
         </is>

--- a/results/job_matches_2026-08-26.xlsx
+++ b/results/job_matches_2026-08-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data AI Engineer - Java</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
+          <t>https://www.indeed.com/viewjob?jk=874c68aa6c38b010</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
+          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Technical Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7d8caa90f5aba1</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Technical Consultant</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CDK Global</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7d8caa90f5aba1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Architect</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>CDK Global</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3282af658369b2af</t>
+          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — Translational Data Products</t>
+          <t>Senior Associate - Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
+          <t>https://www.indeed.com/viewjob?jk=3282af658369b2af</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Java Engineer | Jersey City, US</t>
+          <t>Senior Data Engineer — Translational Data Products</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
+          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Java Engineer | Plano/Columbus, US</t>
+          <t>Java Engineer | Jersey City, US</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Java Engineer | Plano/Columbus, US</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Evolve vacation rentals</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
+          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Revenue)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zuora</t>
+          <t>Evolve vacation rentals</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
+          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer (Revenue)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Zuora</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
+          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ab440c93bda25b</t>
+          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf2c8858d372138</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ab440c93bda25b</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08a226425e0c1a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=abf2c8858d372138</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
+          <t>https://www.indeed.com/viewjob?jk=08a226425e0c1a0f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
+          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 2</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
+          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
+          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Integration &amp; API Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fb1a89b2f01b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Integration &amp; API Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Benda Infotech</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,19 +2351,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a7e25c97039733</t>
+          <t>https://www.indeed.com/viewjob?jk=96fb1a89b2f01b9f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Benda Infotech</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b83410cfb11a99d</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a7e25c97039733</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps &amp; Platform Engineer - Remote Role</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
+          <t>https://www.indeed.com/viewjob?jk=2b83410cfb11a99d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>DevOps &amp; Platform Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
+          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Whiteland, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
+          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Whiteland, IN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
+          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer with Azure Databricks</t>
+          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Aurum Groups</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
+          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Sr. Data Engineer with Azure Databricks</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Praia Health</t>
+          <t>Aurum Groups</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
+          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Praia Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Business Intelligence Developer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Gopher Resource, LLC</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
+          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
+          <t>Data Platform &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Gopher Resource, LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
+          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SQL Database Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BMR infotek</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
+          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
+          <t>SQL Database Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BMR infotek</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Epik Solutions</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Epik Solutions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
+          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,19 +3051,19 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
+          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
+          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Data Architecture)</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, dbt</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aed55033a852ae</t>
+          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Data Engineer (Data Architecture)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
+          <t>https://www.indeed.com/viewjob?jk=46aed55033a852ae</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,24 +3216,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,42 +3286,42 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
+          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
+          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Solutions developer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Engineering and Automation , Aerospace &amp; Defense</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Data Solutions developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Engineering and Automation , Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Platform Engineer (175364)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
+          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Platform Engineer (175364)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TheGuarantors</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
+          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>TheGuarantors</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
+          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Developer / Data Solutions Developer</t>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer II - ML and Observability</t>
+          <t>Software Developer / Data Solutions Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
+          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
         </is>
       </c>
     </row>
@@ -3863,25 +3863,25 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Controller Transformation Analyst</t>
+          <t>Software Engineer II - ML and Observability</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
+          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
+          <t>Controller Transformation Analyst</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>INFINITY HOME SERVICES</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
+          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Jean Martin</t>
+          <t>INFINITY HOME SERVICES</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Jean Martin</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
+          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AI Agentic Software Engineer</t>
+          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
+          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Developer Senior</t>
+          <t>AI Agentic Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>City of Charlotte, NC</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,15 +4161,50 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Software Developer Senior</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>City of Charlotte, NC</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a8009ac0fbc46342</t>
         </is>

--- a/results/job_matches_2026-08-26.xlsx
+++ b/results/job_matches_2026-08-26.xlsx
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Sr Talend Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=451eef560601ded5</t>
+          <t>https://www.indeed.com/viewjob?jk=743665ae918f4a0c</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3ee7b1db2cccd5</t>
+          <t>https://www.indeed.com/viewjob?jk=451eef560601ded5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20d1d5763df13b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3ee7b1db2cccd5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03deb24662c2d57b</t>
+          <t>https://www.indeed.com/viewjob?jk=20d1d5763df13b0f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f191710314c15359</t>
+          <t>https://www.indeed.com/viewjob?jk=03deb24662c2d57b</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d939da0bcff1af</t>
+          <t>https://www.indeed.com/viewjob?jk=f191710314c15359</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e2c8f86b9525b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d939da0bcff1af</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=082b971e34568c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e2c8f86b9525b8</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vista, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d52f1deebd9cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=082b971e34568c1f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Talend Data Engineer</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Vista, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743665ae918f4a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=26d52f1deebd9cc0</t>
         </is>
       </c>
     </row>
@@ -1343,52 +1343,52 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Windsor Mill, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Index Analytics LLC</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Windsor Mill, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0e151be0bbb235</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0e151be0bbb235</t>
+          <t>https://www.indeed.com/viewjob?jk=cc8011b3d20c58b9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8011b3d20c58b9</t>
+          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
         </is>
       </c>
     </row>
@@ -1518,52 +1518,52 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
+          <t>Senior Data AI Engineer - Java</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
+          <t>https://www.indeed.com/viewjob?jk=874c68aa6c38b010</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer - Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874c68aa6c38b010</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Technical Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7d8caa90f5aba1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Technical Consultant</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CDK Global</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7d8caa90f5aba1</t>
+          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Associate - Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CDK Global</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=3282af658369b2af</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Architect</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3282af658369b2af</t>
+          <t>https://www.indeed.com/viewjob?jk=5087fc206cc0738e</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Java Engineer | Jersey City, US</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
+          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Java Engineer | Plano/Columbus, US</t>
+          <t>Java Engineer | Jersey City, US</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Java Engineer | Plano/Columbus, US</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Revenue)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Zuora</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
+          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
+          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
+          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 2</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
+          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Revenue)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Zuora</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
+          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps &amp; Platform Engineer - Remote Role</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Whiteland, IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
+          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>Sr. Data Engineer with Azure Databricks</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Aurum Groups</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
+          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Praia Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
+          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Whiteland, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
+          <t>DevOps &amp; Platform Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer with Azure Databricks</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Aurum Groups</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
+          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Praia Health</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
+          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
+          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SQL Database Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BMR infotek</t>
+          <t>Epik Solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
+          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Epik Solutions</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
+          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>SQL Database Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>BMR infotek</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,19 +3051,19 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
+          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
+          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
+          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,24 +3216,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
+          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
         </is>
       </c>
     </row>
@@ -3338,17 +3338,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Data Solutions developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Engineering and Automation , Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
+          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Platform Engineer (175364)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
+          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Solutions developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Engineering and Automation , Aerospace &amp; Defense</t>
+          <t>TheGuarantors</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
+          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Platform Engineer (175364)</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TheGuarantors</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Software Engineer II - ML and Observability</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
+          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer II - ML and Observability</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
+          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-26.xlsx
+++ b/results/job_matches_2026-08-26.xlsx
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Talend Data Engineer</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743665ae918f4a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=451eef560601ded5</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=451eef560601ded5</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3ee7b1db2cccd5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3ee7b1db2cccd5</t>
+          <t>https://www.indeed.com/viewjob?jk=20d1d5763df13b0f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20d1d5763df13b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=03deb24662c2d57b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03deb24662c2d57b</t>
+          <t>https://www.indeed.com/viewjob?jk=f191710314c15359</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f191710314c15359</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d939da0bcff1af</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d939da0bcff1af</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e2c8f86b9525b8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e2c8f86b9525b8</t>
+          <t>https://www.indeed.com/viewjob?jk=082b971e34568c1f</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Vista, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=082b971e34568c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=26d52f1deebd9cc0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Sr Talend Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vista, CA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d52f1deebd9cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=743665ae918f4a0c</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
+          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
+          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
+          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Java Engineer | Jersey City, US</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Java Engineer | Jersey City, US</t>
+          <t>Java Engineer | Plano/Columbus, US</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
+          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Java Engineer | Plano/Columbus, US</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
+          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Revenue)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Zuora</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
+          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
+          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 2</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
+          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
+          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Revenue)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Zuora</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>DevOps &amp; Platform Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Whiteland, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer with Azure Databricks</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Aurum Groups</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
+          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Praia Health</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
+          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Whiteland, IN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
+          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps &amp; Platform Engineer - Remote Role</t>
+          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
+          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>Sr. Data Engineer with Azure Databricks</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Aurum Groups</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
+          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Praia Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
+          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
+          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
+          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
+          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
+          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>SQL Database Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Epik Solutions</t>
+          <t>BMR infotek</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Epik Solutions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
+          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
+          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SQL Database Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BMR infotek</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,19 +3051,19 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
+          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
+          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
+          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,24 +3216,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
@@ -3338,17 +3338,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Solutions developer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Engineering and Automation , Aerospace &amp; Defense</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Platform Engineer (175364)</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TheGuarantors</t>
+          <t>Engineering and Automation , Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
+          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
+          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Platform Engineer (175364)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>TheGuarantors</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
+          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer II - ML and Observability</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
+          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Software Engineer II - ML and Observability</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
+          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-26.xlsx
+++ b/results/job_matches_2026-08-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Sr Talend Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=451eef560601ded5</t>
+          <t>https://www.indeed.com/viewjob?jk=743665ae918f4a0c</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3ee7b1db2cccd5</t>
+          <t>https://www.indeed.com/viewjob?jk=451eef560601ded5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20d1d5763df13b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3ee7b1db2cccd5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03deb24662c2d57b</t>
+          <t>https://www.indeed.com/viewjob?jk=20d1d5763df13b0f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f191710314c15359</t>
+          <t>https://www.indeed.com/viewjob?jk=03deb24662c2d57b</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d939da0bcff1af</t>
+          <t>https://www.indeed.com/viewjob?jk=f191710314c15359</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e2c8f86b9525b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d939da0bcff1af</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=082b971e34568c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e2c8f86b9525b8</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vista, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d52f1deebd9cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=082b971e34568c1f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Talend Data Engineer</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Vista, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743665ae918f4a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=26d52f1deebd9cc0</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
+          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Revenue)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Zuora</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
+          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
+          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
+          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 2</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
+          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Revenue)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Zuora</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
+          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
+          <t>https://www.indeed.com/viewjob?jk=ca683f10163f215e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SQL Database Engineer</t>
+          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BMR infotek</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
+          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Epik Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
+          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Epik Solutions</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
+          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>SQL Database Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>BMR infotek</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
         </is>
       </c>
     </row>
@@ -3163,17 +3163,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Data Architecture)</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, dbt</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aed55033a852ae</t>
+          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Data Engineer (Data Architecture)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
+          <t>https://www.indeed.com/viewjob?jk=46aed55033a852ae</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,24 +3251,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,42 +3321,42 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Data Solutions developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Engineering and Automation , Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Platform Engineer (175364)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Solutions developer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Engineering and Automation , Aerospace &amp; Defense</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>TheGuarantors</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
+          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Platform Engineer (175364)</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
+          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TheGuarantors</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>Hyland</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
+          <t>https://www.indeed.com/viewjob?jk=f3cb901e68315ba1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Developer / Data Solutions Developer</t>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer II - ML and Observability</t>
+          <t>Software Developer / Data Solutions Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
+          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Controller Transformation Analyst</t>
+          <t>Software Engineer II - ML and Observability</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
+          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,94 +3961,94 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer II, Fintech</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>INFINITY HOME SERVICES</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
+          <t>https://www.indeed.com/viewjob?jk=c724ec5809ede378</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II, Fintech</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Jean Martin</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+          <t>https://www.indeed.com/viewjob?jk=71ec45fe0952b39c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+          <t>Controller Transformation Analyst</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
+          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>INFINITY HOME SERVICES</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
+          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AI Agentic Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Jean Martin</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
+          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Developer Senior</t>
+          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>City of Charlotte, NC</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,15 +4196,155 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Java Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>AI Agentic Software Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Software Developer Senior</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>City of Charlotte, NC</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a8009ac0fbc46342</t>
         </is>

--- a/results/job_matches_2026-08-26.xlsx
+++ b/results/job_matches_2026-08-26.xlsx
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Talend Data Engineer</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743665ae918f4a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=451eef560601ded5</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=451eef560601ded5</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3ee7b1db2cccd5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3ee7b1db2cccd5</t>
+          <t>https://www.indeed.com/viewjob?jk=20d1d5763df13b0f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20d1d5763df13b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=03deb24662c2d57b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03deb24662c2d57b</t>
+          <t>https://www.indeed.com/viewjob?jk=f191710314c15359</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f191710314c15359</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d939da0bcff1af</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d939da0bcff1af</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e2c8f86b9525b8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e2c8f86b9525b8</t>
+          <t>https://www.indeed.com/viewjob?jk=082b971e34568c1f</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Vista, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=082b971e34568c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=26d52f1deebd9cc0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Sr Talend Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vista, CA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d52f1deebd9cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=743665ae918f4a0c</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
+          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,24 +1606,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Technical Consultant</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7d8caa90f5aba1</t>
+          <t>https://www.indeed.com/viewjob?jk=5087fc206cc0738e</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Technical Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5087fc206cc0738e</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7d8caa90f5aba1</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Revenue)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Zuora</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
+          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
+          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 2</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
+          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
+          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Revenue)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Zuora</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Integration &amp; API Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>Benda Infotech</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,19 +2351,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fb1a89b2f01b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a7e25c97039733</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Benda Infotech</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a7e25c97039733</t>
+          <t>https://www.indeed.com/viewjob?jk=2b83410cfb11a99d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Integration &amp; API Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b83410cfb11a99d</t>
+          <t>https://www.indeed.com/viewjob?jk=96fb1a89b2f01b9f</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca683f10163f215e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
+          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
+          <t>SQL Database Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>BMR infotek</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Epik Solutions</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
+          <t>https://www.indeed.com/viewjob?jk=ca683f10163f215e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Epik Solutions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
+          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
+          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SQL Database Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BMR infotek</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
+          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
+          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
+          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
         </is>
       </c>
     </row>
@@ -3373,17 +3373,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Solutions developer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Engineering and Automation , Aerospace &amp; Defense</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Platform Engineer (175364)</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TheGuarantors</t>
+          <t>Engineering and Automation , Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
+          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
+          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Platform Engineer (175364)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>TheGuarantors</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
+          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Hyland</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3cb901e68315ba1</t>
+          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>Hyland</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
+          <t>https://www.indeed.com/viewjob?jk=f3cb901e68315ba1</t>
         </is>
       </c>
     </row>
@@ -3898,17 +3898,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer II - ML and Observability</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
+          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Software Engineer II - ML and Observability</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
+          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
         </is>
       </c>
     </row>
@@ -4213,17 +4213,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>AI Agentic Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
+          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI Agentic Software Engineer</t>
+          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
+          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-26.xlsx
+++ b/results/job_matches_2026-08-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0e151be0bbb235</t>
+          <t>https://www.indeed.com/viewjob?jk=cc8011b3d20c58b9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8011b3d20c58b9</t>
+          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
         </is>
       </c>
     </row>
@@ -1483,52 +1483,52 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
+          <t>Senior Data AI Engineer - Java</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
+          <t>https://www.indeed.com/viewjob?jk=874c68aa6c38b010</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer - Java</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874c68aa6c38b010</t>
+          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>CDK Global</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Associate - Data Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5087fc206cc0738e</t>
+          <t>https://www.indeed.com/viewjob?jk=3282af658369b2af</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CDK Global</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=5087fc206cc0738e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Architect</t>
+          <t>Senior Data Engineer — Translational Data Products</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3282af658369b2af</t>
+          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Technical Consultant</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7d8caa90f5aba1</t>
+          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — Translational Data Products</t>
+          <t>Java Engineer | Jersey City, US</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Java Engineer | Jersey City, US</t>
+          <t>Java Engineer | Plano/Columbus, US</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
+          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Java Engineer | Plano/Columbus, US</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Evolve vacation rentals</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
+          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Software Engineer (Revenue)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Zuora</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Evolve vacation rentals</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
+          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Revenue)</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Zuora</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ab440c93bda25b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
+          <t>https://www.indeed.com/viewjob?jk=abf2c8858d372138</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ab440c93bda25b</t>
+          <t>https://www.indeed.com/viewjob?jk=08a226425e0c1a0f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf2c8858d372138</t>
+          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08a226425e0c1a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
+          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
+          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Integration &amp; API Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=96fb1a89b2f01b9f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Benda Infotech</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,19 +2316,19 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a7e25c97039733</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Benda Infotech</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a7e25c97039733</t>
+          <t>https://www.indeed.com/viewjob?jk=2b83410cfb11a99d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b83410cfb11a99d</t>
+          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Integration &amp; API Architect</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fb1a89b2f01b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps &amp; Platform Engineer - Remote Role</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Whiteland, IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
+          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6e427e88678150</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>DevOps &amp; Platform Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Whiteland, IN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
+          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
+          <t>Sr. Data Engineer with Azure Databricks</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Aurum Groups</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
+          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer with Azure Databricks</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Aurum Groups</t>
+          <t>Praia Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
+          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Praia Health</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
+          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
+          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Business Intelligence Developer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Gopher Resource, LLC</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
+          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
+          <t>SQL Database Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>BMR infotek</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
+          <t>https://www.indeed.com/viewjob?jk=ca683f10163f215e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SQL Database Engineer</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BMR infotek</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Epik Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca683f10163f215e</t>
+          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Epik Solutions</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
+          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
+          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
+          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Data Architecture)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
+          <t>https://www.indeed.com/viewjob?jk=46aed55033a852ae</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Data Architecture)</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, dbt</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aed55033a852ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,77 +3286,77 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
+          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Data Solutions developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Engineering and Automation , Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Solutions developer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Engineering and Automation , Aerospace &amp; Defense</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Platform Engineer (175364)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
+          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Platform Engineer (175364)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>TheGuarantors</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
+          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hyland</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=f3cb901e68315ba1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TheGuarantors</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
+          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
+          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Software Developer / Data Solutions Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Hyland</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3cb901e68315ba1</t>
+          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Developer / Data Solutions Developer</t>
+          <t>Software Engineer II - ML and Observability</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Software Engineer II, Fintech</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
+          <t>https://www.indeed.com/viewjob?jk=c724ec5809ede378</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer II - ML and Observability</t>
+          <t>Software Engineer II, Fintech</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,104 +3951,104 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
+          <t>https://www.indeed.com/viewjob?jk=71ec45fe0952b39c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer II, Fintech</t>
+          <t>Controller Transformation Analyst</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c724ec5809ede378</t>
+          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer II, Fintech</t>
+          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ec45fe0952b39c</t>
+          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Controller Transformation Analyst</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>INFINITY HOME SERVICES</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
+          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
+          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Jean Martin</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>INFINITY HOME SERVICES</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
+          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Jean Martin</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Software Developer Senior</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>City of Charlotte, NC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4275,76 +4275,6 @@
         </is>
       </c>
       <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>LTM Limited</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Software Developer Senior</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>City of Charlotte, NC</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a8009ac0fbc46342</t>
         </is>

--- a/results/job_matches_2026-08-26.xlsx
+++ b/results/job_matches_2026-08-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,60 +853,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AWS Python Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>ProArch</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834d52dff47fe0c1</t>
+          <t>https://www.indeed.com/viewjob?jk=08c354cd10dc0d65</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Python Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Peoples Gas System</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32754dc82fcb92a</t>
+          <t>https://www.indeed.com/viewjob?jk=834d52dff47fe0c1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, Data Management</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Peoples Gas System</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed5484e209306fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=d32754dc82fcb92a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Systems Engineer, Data Management</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Premier Nutrition Company</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bf2e42812735206</t>
+          <t>https://www.indeed.com/viewjob?jk=ed5484e209306fd8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AAA Auto Club Enterprises</t>
+          <t>Premier Nutrition Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e80b460b21ce73</t>
+          <t>https://www.indeed.com/viewjob?jk=7bf2e42812735206</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+          <t>Senior Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>AAA Auto Club Enterprises</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e80b460b21ce73</t>
         </is>
       </c>
     </row>
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
+          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OneDome</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,77 +1116,77 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, BigQuery</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e7886502273f96</t>
+          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>OneDome</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, BigQuery</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=16e7886502273f96</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edcca601c37b3df4</t>
+          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c6800ab3996b5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=edcca601c37b3df4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineering Summer Intern (May-Aug '27)</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f0b99fc7578c909</t>
+          <t>https://www.indeed.com/viewjob?jk=1c6800ab3996b5b3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
+          <t>Data Engineering Summer Intern (May-Aug '27)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4bc1c52db1db4e</t>
+          <t>https://www.indeed.com/viewjob?jk=3f0b99fc7578c909</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4bc1c52db1db4e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Index Analytics LLC</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Windsor Mill, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
+          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Windsor Mill, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8011b3d20c58b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
+          <t>https://www.indeed.com/viewjob?jk=cc8011b3d20c58b9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
+          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer - Java</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874c68aa6c38b010</t>
+          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data AI Engineer - Java</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
+          <t>https://www.indeed.com/viewjob?jk=874c68aa6c38b010</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
+          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CDK Global</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Architect</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>CDK Global</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3282af658369b2af</t>
+          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Associate - Data Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5087fc206cc0738e</t>
+          <t>https://www.indeed.com/viewjob?jk=3282af658369b2af</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — Translational Data Products</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
+          <t>https://www.indeed.com/viewjob?jk=5087fc206cc0738e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Data Engineer — Translational Data Products</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Java Engineer | Jersey City, US</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
+          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Java Engineer | Plano/Columbus, US</t>
+          <t>Java Engineer | Jersey City, US</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Engineer | Plano/Columbus, US</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Evolve vacation rentals</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Revenue)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Zuora</t>
+          <t>Evolve vacation rentals</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
+          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer (Revenue)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Zuora</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
+          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ab440c93bda25b</t>
+          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf2c8858d372138</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ab440c93bda25b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08a226425e0c1a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=abf2c8858d372138</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
+          <t>https://www.indeed.com/viewjob?jk=08a226425e0c1a0f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
+          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 2</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
+          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
+          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Integration &amp; API Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fb1a89b2f01b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Integration &amp; API Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Benda Infotech</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,19 +2316,19 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a7e25c97039733</t>
+          <t>https://www.indeed.com/viewjob?jk=96fb1a89b2f01b9f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Benda Infotech</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b83410cfb11a99d</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a7e25c97039733</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
+          <t>https://www.indeed.com/viewjob?jk=2b83410cfb11a99d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
+          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Whiteland, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
+          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Whiteland, IN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6e427e88678150</t>
+          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps &amp; Platform Engineer - Remote Role</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6e427e88678150</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
+          <t>DevOps &amp; Platform Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer with Azure Databricks</t>
+          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Aurum Groups</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
+          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Sr. Data Engineer with Azure Databricks</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Praia Health</t>
+          <t>Aurum Groups</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
+          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Praia Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
+          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
+          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SQL Database Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BMR infotek</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
+          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>SQL Database Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>BMR infotek</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca683f10163f215e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ca683f10163f215e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Epik Solutions</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Epik Solutions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
+          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,19 +3051,19 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
+          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
+          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Data Architecture)</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, dbt</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aed55033a852ae</t>
+          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Data Engineer (Data Architecture)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
+          <t>https://www.indeed.com/viewjob?jk=46aed55033a852ae</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,24 +3216,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer II - ML and Observability</t>
+          <t>Software Engineer II, Fintech</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
+          <t>https://www.indeed.com/viewjob?jk=c724ec5809ede378</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,59 +3926,59 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c724ec5809ede378</t>
+          <t>https://www.indeed.com/viewjob?jk=71ec45fe0952b39c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer II, Fintech</t>
+          <t>Controller Transformation Analyst</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ec45fe0952b39c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Controller Transformation Analyst</t>
+          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
+          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>INFINITY HOME SERVICES</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
+          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>INFINITY HOME SERVICES</t>
+          <t>Jean Martin</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Jean Martin</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+          <t>https://www.indeed.com/viewjob?jk=2b9ca78d46c32c41</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
+          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
+          <t>AI Agentic Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
+          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AI Agentic Software Engineer</t>
+          <t>Software Developer Senior</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>City of Charlotte, NC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4240,41 +4240,6 @@
         </is>
       </c>
       <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Software Developer Senior</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>City of Charlotte, NC</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a8009ac0fbc46342</t>
         </is>

--- a/results/job_matches_2026-08-26.xlsx
+++ b/results/job_matches_2026-08-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>OneDome</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,112 +1081,112 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, BigQuery</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=16e7886502273f96</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc1f3e73c9d5ec1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OneDome</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, BigQuery</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e7886502273f96</t>
+          <t>https://www.indeed.com/viewjob?jk=edcca601c37b3df4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=1c6800ab3996b5b3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Engineering Summer Intern (May-Aug '27)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edcca601c37b3df4</t>
+          <t>https://www.indeed.com/viewjob?jk=3f0b99fc7578c909</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c6800ab3996b5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4bc1c52db1db4e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineering Summer Intern (May-Aug '27)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Windsor Mill, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f0b99fc7578c909</t>
+          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
+          <t>SAP BTP CPI integration developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>www.prolim.com</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4bc1c52db1db4e</t>
+          <t>https://www.indeed.com/viewjob?jk=59b9d3edeebc6d93</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
+          <t>https://www.indeed.com/viewjob?jk=cc8011b3d20c58b9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Index Analytics LLC</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Windsor Mill, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
+          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Data AI Engineer - Java</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8011b3d20c58b9</t>
+          <t>https://www.indeed.com/viewjob?jk=874c68aa6c38b010</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
+          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer - Java</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>CDK Global</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874c68aa6c38b010</t>
+          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Associate - Data Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
+          <t>https://www.indeed.com/viewjob?jk=3282af658369b2af</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
+          <t>https://www.indeed.com/viewjob?jk=5087fc206cc0738e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer — Translational Data Products</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CDK Global</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Architect</t>
+          <t>Java Engineer | Jersey City, US</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3282af658369b2af</t>
+          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Java Engineer | Plano/Columbus, US</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5087fc206cc0738e</t>
+          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — Translational Data Products</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, ETL</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
+          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Evolve vacation rentals</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Java Engineer | Jersey City, US</t>
+          <t>Senior Software Engineer (Revenue)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Zuora</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
+          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Java Engineer | Plano/Columbus, US</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
+          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Evolve vacation rentals</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ab440c93bda25b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Revenue)</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zuora</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,19 +1931,19 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
+          <t>https://www.indeed.com/viewjob?jk=abf2c8858d372138</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
+          <t>https://www.indeed.com/viewjob?jk=08a226425e0c1a0f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ab440c93bda25b</t>
+          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf2c8858d372138</t>
+          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08a226425e0c1a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
+          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
+          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Senior IT Programmer Analyst</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Jupiter, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b92ef7334fb5aa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Benda Infotech</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a7e25c97039733</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
+          <t>https://www.indeed.com/viewjob?jk=2b83410cfb11a99d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Integration &amp; API Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, ETL</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fb1a89b2f01b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6e427e88678150</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps &amp; Platform Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Benda Infotech</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a7e25c97039733</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b83410cfb11a99d</t>
+          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
+          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Whiteland, IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
+          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Whiteland, IN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
+          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Data Engineer with Azure Databricks</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Aurum Groups</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6e427e88678150</t>
+          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps &amp; Platform Engineer - Remote Role</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Praia Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
+          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
+          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer with Azure Databricks</t>
+          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Aurum Groups</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
+          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Praia Health</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
+          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>SQL Database Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>BMR infotek</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>MetTel</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
+          <t>https://www.indeed.com/viewjob?jk=7cdad9aa5658efec</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
+          <t>https://www.indeed.com/viewjob?jk=ca683f10163f215e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SQL Database Engineer</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BMR infotek</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Epik Solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca683f10163f215e</t>
+          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Epik Solutions</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
+          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
+          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
+          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Data Architecture)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
+          <t>https://www.indeed.com/viewjob?jk=46aed55033a852ae</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Data Architecture)</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, dbt</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aed55033a852ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,77 +3226,77 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
+          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
+          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Data Solutions developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Engineering and Automation , Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
+          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
+          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Solutions developer</t>
+          <t>Platform Engineer (175364)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Engineering and Automation , Aerospace &amp; Defense</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>TheGuarantors</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
+          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Platform Engineer (175364)</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Hyland</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
+          <t>https://www.indeed.com/viewjob?jk=f3cb901e68315ba1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Software Developer / Data Solutions Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TheGuarantors</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
+          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Hyland</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3cb901e68315ba1</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+          <t>Software Engineer II, Fintech</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
+          <t>https://www.indeed.com/viewjob?jk=c724ec5809ede378</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Software Engineer II, Fintech</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,42 +3811,42 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
+          <t>https://www.indeed.com/viewjob?jk=71ec45fe0952b39c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Developer / Data Solutions Developer</t>
+          <t>Controller Transformation Analyst</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,94 +3856,94 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer II, Fintech</t>
+          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c724ec5809ede378</t>
+          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer II, Fintech</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>INFINITY HOME SERVICES</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ec45fe0952b39c</t>
+          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Controller Transformation Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
+          <t>https://www.indeed.com/viewjob?jk=2b9ca78d46c32c41</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
+          <t>AI Agentic Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,19 +3996,19 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
+          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>INFINITY HOME SERVICES</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
+          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer Senior</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Jean Martin</t>
+          <t>City of Charlotte, NC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4065,181 +4065,6 @@
         </is>
       </c>
       <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9ca78d46c32c41</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>AWS Data Architect (Senior Specialist - Cloud Engineering)</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>LTM Limited</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, RDS, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b57dd648ed3249a</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>AI Agentic Software Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Siemens</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Software Developer Senior</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>City of Charlotte, NC</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a8009ac0fbc46342</t>
         </is>

--- a/results/job_matches_2026-08-26.xlsx
+++ b/results/job_matches_2026-08-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Sr Talend Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=451eef560601ded5</t>
+          <t>https://www.indeed.com/viewjob?jk=743665ae918f4a0c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>ProArch</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3ee7b1db2cccd5</t>
+          <t>https://www.indeed.com/viewjob?jk=08c354cd10dc0d65</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>Peoples Gas System</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20d1d5763df13b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=d32754dc82fcb92a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Senior Database Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Woodlawn, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03deb24662c2d57b</t>
+          <t>https://www.indeed.com/viewjob?jk=da35022772d82448</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Senior Systems Engineer, Data Management</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f191710314c15359</t>
+          <t>https://www.indeed.com/viewjob?jk=ed5484e209306fd8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Senior Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>AAA Auto Club Enterprises</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,207 +671,207 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d939da0bcff1af</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e80b460b21ce73</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e2c8f86b9525b8</t>
+          <t>https://www.indeed.com/viewjob?jk=124139dc71cb3de3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.1</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=082b971e34568c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=909a1f6b26c17925</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vista, CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20.1</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d52f1deebd9cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=c93acac401ad3bbf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Talend Data Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>20.1</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743665ae918f4a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=94f4a28dfa9476bc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Analytics)</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19.4</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=181a31f219accf44</t>
+          <t>https://www.indeed.com/viewjob?jk=13f55062141bc024</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ProArch</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,129 +881,129 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c354cd10dc0d65</t>
+          <t>https://www.indeed.com/viewjob?jk=93208e2f6926347a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS Python Data Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834d52dff47fe0c1</t>
+          <t>https://www.indeed.com/viewjob?jk=7eea24c2a0ab6c8d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Peoples Gas System</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32754dc82fcb92a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b928b70f880f43e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, Data Management</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed5484e209306fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=c53c3f82e674c498</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Premier Nutrition Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bf2e42812735206</t>
+          <t>https://www.indeed.com/viewjob?jk=52c28366a273c1cc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AAA Auto Club Enterprises</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e80b460b21ce73</t>
+          <t>https://www.indeed.com/viewjob?jk=b120619fc2e804f7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OneDome</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, BigQuery</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e7886502273f96</t>
+          <t>https://www.indeed.com/viewjob?jk=9da89a063f9c8521</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,207 +1126,207 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc1f3e73c9d5ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1b6aefc05efd92</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edcca601c37b3df4</t>
+          <t>https://www.indeed.com/viewjob?jk=b821791df6fb974a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c6800ab3996b5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=e73a1e57486a0c1d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineering Summer Intern (May-Aug '27)</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f0b99fc7578c909</t>
+          <t>https://www.indeed.com/viewjob?jk=a17a59c378aa6173</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4bc1c52db1db4e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ce6fa4c0175733b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Index Analytics LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Windsor Mill, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
+          <t>https://www.indeed.com/viewjob?jk=2328e655f3e8d78f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SAP BTP CPI integration developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>www.prolim.com</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,102 +1336,102 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59b9d3edeebc6d93</t>
+          <t>https://www.indeed.com/viewjob?jk=a81d7d772ab85759</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8011b3d20c58b9</t>
+          <t>https://www.indeed.com/viewjob?jk=526ba6cf1cb5f265</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
+          <t>https://www.indeed.com/viewjob?jk=1925f45d961a4413</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer - Java</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874c68aa6c38b010</t>
+          <t>https://www.indeed.com/viewjob?jk=345d49ceaf51b3dd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
+          <t>https://www.indeed.com/viewjob?jk=4237b23eb5e0e0e4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,102 +1511,102 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
+          <t>https://www.indeed.com/viewjob?jk=342cda44215c91c6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CDK Global</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=27914ea323041751</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Architect</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3282af658369b2af</t>
+          <t>https://www.indeed.com/viewjob?jk=9fce442c2387b717</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,592 +1616,592 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5087fc206cc0738e</t>
+          <t>https://www.indeed.com/viewjob?jk=27ca7d2c6b1b746c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — Translational Data Products</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, ETL</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
+          <t>https://www.indeed.com/viewjob?jk=36418ba6cc0c14c2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Java Engineer | Jersey City, US</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
+          <t>https://www.indeed.com/viewjob?jk=af4943f5569a0767</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Java Engineer | Plano/Columbus, US</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b4f3ef2e79895a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d271a63d05bf0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Evolve vacation rentals</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
+          <t>https://www.indeed.com/viewjob?jk=00aac80eaaee8a4a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Revenue)</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Zuora</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
+          <t>https://www.indeed.com/viewjob?jk=a89e649b137768be</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
+          <t>https://www.indeed.com/viewjob?jk=38c7ac9df441601c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ab440c93bda25b</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4418551c98d3ec</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf2c8858d372138</t>
+          <t>https://www.indeed.com/viewjob?jk=8f19d7d7cf4d3ecc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08a226425e0c1a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=9041cb7d9adbbd88</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb22c28a20aec81</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a01a365ccb6479</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 2</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
+          <t>https://www.indeed.com/viewjob?jk=197c01a921c0f589</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=a3fff2959c75f6c5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=d40d369719872875</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
+          <t>https://www.indeed.com/viewjob?jk=53a1b379b0810dfc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior IT Programmer Analyst</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, PostgreSQL</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,102 +2211,102 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b92ef7334fb5aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4bcbf3821afe5c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Benda Infotech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a7e25c97039733</t>
+          <t>https://www.indeed.com/viewjob?jk=32734f2534389aff</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b83410cfb11a99d</t>
+          <t>https://www.indeed.com/viewjob?jk=2430a8d9cbfed099</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,277 +2316,277 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6e427e88678150</t>
+          <t>https://www.indeed.com/viewjob?jk=026ee3ac609c3551</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevOps &amp; Platform Engineer - Remote Role</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
+          <t>https://www.indeed.com/viewjob?jk=762089df3fb6872a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
+          <t>https://www.indeed.com/viewjob?jk=d788e97a3bd89302</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
+          <t>https://www.indeed.com/viewjob?jk=60b50bb9dfbb5aa1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Whiteland, IN, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
+          <t>https://www.indeed.com/viewjob?jk=8f36a75009e4ba82</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>OneDome</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, BigQuery</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
+          <t>https://www.indeed.com/viewjob?jk=16e7886502273f96</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer with Azure Databricks</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Aurum Groups</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>S3, IAM, RDS, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
+          <t>https://www.indeed.com/viewjob?jk=a001f2cdcb66bc68</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Praia Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc1f3e73c9d5ec1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
+          <t>https://www.indeed.com/viewjob?jk=edcca601c37b3df4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
+          <t>https://www.indeed.com/viewjob?jk=1c6800ab3996b5b3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineering Summer Intern (May-Aug '27)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
+          <t>https://www.indeed.com/viewjob?jk=3f0b99fc7578c909</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SQL Database Engineer</t>
+          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BMR infotek</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,102 +2701,102 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4bc1c52db1db4e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MetTel</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Windsor Mill, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cdad9aa5658efec</t>
+          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>SAP BTP CPI integration developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>www.prolim.com</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca683f10163f215e</t>
+          <t>https://www.indeed.com/viewjob?jk=59b9d3edeebc6d93</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
+          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
+          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data AI Engineer - Java</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Epik Solutions</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
+          <t>https://www.indeed.com/viewjob?jk=874c68aa6c38b010</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,54 +2876,54 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>CDK Global</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2932,11 +2932,11 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,19 +2946,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Associate - Data Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2967,46 +2967,46 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
+          <t>https://www.indeed.com/viewjob?jk=3282af658369b2af</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer — Translational Data Products</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
+          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,120 +3033,120 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
+          <t>https://www.indeed.com/viewjob?jk=5087fc206cc0738e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Java Engineer | Jersey City, US</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
+          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Data Architecture)</t>
+          <t>Java Engineer | Plano/Columbus, US</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aed55033a852ae</t>
+          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,67 +3156,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
+          <t>https://www.indeed.com/viewjob?jk=5fbf73e2a2d7e581</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
+          <t>https://www.indeed.com/viewjob?jk=66a5f3320c6af81a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9f00ed4d637eba</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Evolve vacation rentals</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
+          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Senior Software Engineer (Revenue)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Zuora</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
+          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,67 +3331,67 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Development Systems Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
+          <t>https://www.indeed.com/viewjob?jk=e24f70ff61678f2e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Solutions developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Engineering and Automation , Aerospace &amp; Defense</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,67 +3471,67 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
+          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Platform Engineer (175364)</t>
+          <t>Senior IT Programmer Analyst</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Jupiter, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b92ef7334fb5aa</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Benda Infotech</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a7e25c97039733</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TheGuarantors</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Whiteland, IN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,19 +3576,19 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
+          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Hyland</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3597,46 +3597,46 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3cb901e68315ba1</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6e427e88678150</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Developer / Data Solutions Developer</t>
+          <t>DevOps &amp; Platform Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
+          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
+          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer II, Fintech</t>
+          <t>Sr Data &amp; AI Solution Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>Grocery Outlet</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,67 +3786,67 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c724ec5809ede378</t>
+          <t>https://www.indeed.com/viewjob?jk=60f0706c31a0334f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer II, Fintech</t>
+          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ec45fe0952b39c</t>
+          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Controller Transformation Analyst</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,67 +3856,67 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
+          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>MetTel</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
+          <t>https://www.indeed.com/viewjob?jk=7cdad9aa5658efec</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>INFINITY HOME SERVICES</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,67 +3926,67 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
+          <t>https://www.indeed.com/viewjob?jk=ca683f10163f215e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9ca78d46c32c41</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI Agentic Software Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Epik Solutions</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
+          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
+          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,40 +4031,1440 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Velir</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Velir</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Velir</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Velir</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Associate - Data Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>New York Life</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Data Architecture)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Wpromote, LLC</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, dbt</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46aed55033a852ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>OMS Medical Billing</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Addison, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure &amp; Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Madison, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c681a9056e23349f</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure &amp; Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bbfa5155595ec72</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Data Solutions developer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Engineering and Automation , Aerospace &amp; Defense</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Cloud Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Zoom Communications</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Platform Engineer (175364)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Sr. Azure Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Lobel Financial</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Anaheim, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0db6ac7cf2f086e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Hyland</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3cb901e68315ba1</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Software Developer 2</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>BLOC Resources, LLC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8f6e507178eea68</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Software Developer / Data Solutions Developer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>4P Consulting Inc.</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Sarnova HC, LLC</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Sarnova HC, LLC</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Dublin, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Databricks Developer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Hanover, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Oracle, ETL, ELT, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a28485007e465c63</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Fintech</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c724ec5809ede378</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Fintech</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71ec45fe0952b39c</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Generative AI Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d1b15647f88acc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Data Engineer BILH Pharmacy Westwood, Ma, Hybrid / on-site</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Beth Israel Lahey Health</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Westwood, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Spark, Scala, Data Modeling, ETL, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf255b6550fc872f</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Sr. Scientific Data Engineer, R&amp;D Data Platform</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Abbott Park, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, RDS, Unity Catalog, Spark</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8280545268f9a67b</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Infrastructure Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Tapestry</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, ECS, IAM, RDS, Azure, Spark, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18a7770f9ee523e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d618dcf278adc42</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cae136048a3d8779</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Connected Vehicle Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Textron Specialized Vehicles</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Augusta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, Scala, ETL, MLOps, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfac0a590ec45dcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Controller Transformation Analyst</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Newark, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64543ec5f02890f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15a494f407d22227</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2546a365f20e983</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7988a3ee97db7900</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b9ca78d46c32c41</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>AI Agentic Software Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Senior Java Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
           <t>Software Developer Senior</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>City of Charlotte, NC</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>Charlotte, NC, US USA</t>
         </is>
       </c>
-      <c r="D104" t="n">
+      <c r="D144" t="n">
         <v>10.4</v>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a8009ac0fbc46342</t>
         </is>

--- a/results/job_matches_2026-08-26.xlsx
+++ b/results/job_matches_2026-08-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Talend Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>United Wheels Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Miamisburg, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743665ae918f4a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=27e79ad2e915711e</t>
         </is>
       </c>
     </row>
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Database Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Peoples Gas System</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Woodlawn, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32754dc82fcb92a</t>
+          <t>https://www.indeed.com/viewjob?jk=da35022772d82448</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Database Architect</t>
+          <t>Senior Systems Engineer, Data Management</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Woodlawn, MD, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,112 +591,112 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da35022772d82448</t>
+          <t>https://www.indeed.com/viewjob?jk=ed5484e209306fd8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, Data Management</t>
+          <t>Java Backend Developer with Digital Banking exp.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed5484e209306fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=975335ad394cec71</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AAA Auto Club Enterprises</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>S3, IAM, RDS, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e80b460b21ce73</t>
+          <t>https://www.indeed.com/viewjob?jk=a001f2cdcb66bc68</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>AWS Connect Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>One Park Financial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,172 +706,172 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=124139dc71cb3de3</t>
+          <t>https://www.indeed.com/viewjob?jk=d70704f843af03d8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909a1f6b26c17925</t>
+          <t>https://www.indeed.com/viewjob?jk=edcca601c37b3df4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93acac401ad3bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=1c6800ab3996b5b3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Data Engineering Summer Intern (May-Aug '27)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f4a28dfa9476bc</t>
+          <t>https://www.indeed.com/viewjob?jk=3f0b99fc7578c909</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f55062141bc024</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4bc1c52db1db4e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Data Engineer Grade C1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93208e2f6926347a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c5adae439689ed8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Windsor Mill, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eea24c2a0ab6c8d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>SAP BTP CPI integration developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>www.prolim.com</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b928b70f880f43e</t>
+          <t>https://www.indeed.com/viewjob?jk=59b9d3edeebc6d93</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53c3f82e674c498</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1337a2df075881</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52c28366a273c1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=601078fca17d6436</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b120619fc2e804f7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb36469ab073779d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Data AI Engineer - Java</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da89a063f9c8521</t>
+          <t>https://www.indeed.com/viewjob?jk=874c68aa6c38b010</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1b6aefc05efd92</t>
+          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wolfe, LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b821791df6fb974a</t>
+          <t>https://www.indeed.com/viewjob?jk=55e8240a360be575</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,137 +1196,137 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73a1e57486a0c1d</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CDK Global</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17a59c378aa6173</t>
+          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Associate - Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ce6fa4c0175733b</t>
+          <t>https://www.indeed.com/viewjob?jk=3282af658369b2af</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Data Engineer — Translational Data Products</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2328e655f3e8d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,102 +1336,102 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a81d7d772ab85759</t>
+          <t>https://www.indeed.com/viewjob?jk=5087fc206cc0738e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Java Engineer | Jersey City, US</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526ba6cf1cb5f265</t>
+          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Java Engineer | Plano/Columbus, US</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1925f45d961a4413</t>
+          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,242 +1441,242 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=345d49ceaf51b3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=d5686a0b8163a717</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4237b23eb5e0e0e4</t>
+          <t>https://www.indeed.com/viewjob?jk=5fbf73e2a2d7e581</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342cda44215c91c6</t>
+          <t>https://www.indeed.com/viewjob?jk=66a5f3320c6af81a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27914ea323041751</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9f00ed4d637eba</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Evolve vacation rentals</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fce442c2387b717</t>
+          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Software Engineer (Revenue)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Zuora</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27ca7d2c6b1b746c</t>
+          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36418ba6cc0c14c2</t>
+          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Development Systems Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,102 +1686,102 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af4943f5569a0767</t>
+          <t>https://www.indeed.com/viewjob?jk=e24f70ff61678f2e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b4f3ef2e79895a</t>
+          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2d271a63d05bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00aac80eaaee8a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=0dca40c7722a95e0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior IT Programmer Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Jupiter, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89e649b137768be</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b92ef7334fb5aa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38c7ac9df441601c</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6e427e88678150</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Benda Infotech</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4418551c98d3ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a7e25c97039733</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Brooklyn, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f19d7d7cf4d3ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=ff9ec8de823c6860</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Software Engineer – Observability, Co-op</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ancestry</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Lambda, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9041cb7d9adbbd88</t>
+          <t>https://www.indeed.com/viewjob?jk=ee144fbb1de80e29</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr Data &amp; AI Solution Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Grocery Outlet</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb22c28a20aec81</t>
+          <t>https://www.indeed.com/viewjob?jk=60f0706c31a0334f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a01a365ccb6479</t>
+          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>MetTel</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,382 +2071,382 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197c01a921c0f589</t>
+          <t>https://www.indeed.com/viewjob?jk=7cdad9aa5658efec</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3fff2959c75f6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ca683f10163f215e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d40d369719872875</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Epik Solutions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a1b379b0810dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4bcbf3821afe5c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32734f2534389aff</t>
+          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2430a8d9cbfed099</t>
+          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=026ee3ac609c3551</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=762089df3fb6872a</t>
+          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d788e97a3bd89302</t>
+          <t>https://www.indeed.com/viewjob?jk=5a46ae133ecb4f7e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60b50bb9dfbb5aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Software Engineer - Full Stack - UI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Swisslog Healthcare AG Branche NL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f36a75009e4ba82</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c9e14eaa0d3f83</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OneDome</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, BigQuery</t>
+          <t>AWS, EMR, Athena, S3, RDS, Databricks, Scala, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e7886502273f96</t>
+          <t>https://www.indeed.com/viewjob?jk=13c3fd73c78e94d5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Data Architecture)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a001f2cdcb66bc68</t>
+          <t>https://www.indeed.com/viewjob?jk=46aed55033a852ae</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Swisslog Healthcare</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,137 +2561,137 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc1f3e73c9d5ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=4301843c7a7136de</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>Pyxis Management Consulting Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edcca601c37b3df4</t>
+          <t>https://www.indeed.com/viewjob?jk=df510917e20222b6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c6800ab3996b5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=c681a9056e23349f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineering Summer Intern (May-Aug '27)</t>
+          <t>Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f0b99fc7578c909</t>
+          <t>https://www.indeed.com/viewjob?jk=7bbfa5155595ec72</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
+          <t>Data Solutions developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>Engineering and Automation , Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,54 +2701,54 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4bc1c52db1db4e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Azure Solutions Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Index Analytics LLC</t>
+          <t>Lobel Financial</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Windsor Mill, MD, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, Scala, Snowflake, DynamoDB, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6cb1b5f667e2d24</t>
+          <t>https://www.indeed.com/viewjob?jk=0db6ac7cf2f086e8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SAP BTP CPI integration developer</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>www.prolim.com</t>
+          <t>Hyland</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2757,116 +2757,116 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59b9d3edeebc6d93</t>
+          <t>https://www.indeed.com/viewjob?jk=f3cb901e68315ba1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
+          <t>Software Developer 2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f6e507178eea68</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer - Java</t>
+          <t>Software Developer / Data Solutions Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874c68aa6c38b010</t>
+          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,172 +2876,172 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aedfe1f2413e05</t>
+          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CDK Global</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Oracle, ETL, ELT, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22ba8fe0ae9d2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=a28485007e465c63</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Architect</t>
+          <t>Software Engineer II, Fintech</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake</t>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3282af658369b2af</t>
+          <t>https://www.indeed.com/viewjob?jk=c724ec5809ede378</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — Translational Data Products</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, MLOps, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd8bdf82d729ef3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,452 +3051,452 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5087fc206cc0738e</t>
+          <t>https://www.indeed.com/viewjob?jk=4d1b15647f88acc1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Java Engineer | Jersey City, US</t>
+          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Charlotte)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae48fe542473d529</t>
+          <t>https://www.indeed.com/viewjob?jk=dbae05545c6868d1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Java Engineer | Plano/Columbus, US</t>
+          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Chicago)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4be7f31f3e7685a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef6f0621a423908c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Data Engineer BILH Pharmacy Westwood, Ma, Hybrid / on-site</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Beth Israel Lahey Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Westwood, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, GCP, Spark, Scala, Data Modeling, ETL, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fbf73e2a2d7e581</t>
+          <t>https://www.indeed.com/viewjob?jk=bf255b6550fc872f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Sr. Scientific Data Engineer, R&amp;D Data Platform</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Abbott Park, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, RDS, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a5f3320c6af81a</t>
+          <t>https://www.indeed.com/viewjob?jk=8280545268f9a67b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Infrastructure Automation Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Tapestry</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Spark, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9f00ed4d637eba</t>
+          <t>https://www.indeed.com/viewjob?jk=18a7770f9ee523e2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Evolve vacation rentals</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT</t>
+          <t>RDS, Databricks, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3d618dcf278adc42</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Revenue)</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Zuora</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Databricks, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
+          <t>https://www.indeed.com/viewjob?jk=cae136048a3d8779</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Connected Vehicle Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Textron Specialized Vehicles</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, MySQL, NoSQL, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, ETL, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b939d93319884ab</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac0a590ec45dcb</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Development Systems Engineer</t>
+          <t>Full Stack Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>Collectiv LLC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e24f70ff61678f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=47e76c61522acf68</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
+          <t>https://www.indeed.com/viewjob?jk=64543ec5f02890f1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
+          <t>https://www.indeed.com/viewjob?jk=15a494f407d22227</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 2</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
+          <t>https://www.indeed.com/viewjob?jk=d2546a365f20e983</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior IT Programmer Analyst</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b92ef7334fb5aa</t>
+          <t>https://www.indeed.com/viewjob?jk=7988a3ee97db7900</t>
         </is>
       </c>
     </row>
@@ -3518,125 +3518,125 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Benda Infotech</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a7e25c97039733</t>
+          <t>https://www.indeed.com/viewjob?jk=2b9ca78d46c32c41</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Full Stack AI Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Freedom Mortgage</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Whiteland, IN, US USA</t>
+          <t>Marlton, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3950e40095baf48</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Agentic Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6e427e88678150</t>
+          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DevOps &amp; Platform Engineer - Remote Role</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
+          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>AI LLM Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
+          <t>https://www.indeed.com/viewjob?jk=512d71dc2c72b295</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>Software Developer Senior</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>City of Charlotte, NC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,1757 +3716,42 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
+          <t>https://www.indeed.com/viewjob?jk=a8009ac0fbc46342</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
+          <t>Senior Application Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>SidhSol</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>S3, RDS, Azure, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Sr Data &amp; AI Solution Architect</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Grocery Outlet</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Emeryville, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60f0706c31a0334f</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Cotiviti</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Blob Storage, Hadoop, Spark, Scala, Oracle, ETL, Power BI, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Thrivent</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Data Platform</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>MetTel</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7cdad9aa5658efec</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Kohl's</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Menomonee Falls, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca683f10163f215e</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Databricks Data Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Epik Solutions</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43eb5d617c39ee62</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Velir</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Velir</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Velir</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Velir</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Velir</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Associate - Data Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>New York Life</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer (Data Architecture)</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Wpromote, LLC</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, dbt</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46aed55033a852ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>AI / ML Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Full Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>OMS Medical Billing</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Addison, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Cloud Infrastructure &amp; Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>PlayStation</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Madison, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c681a9056e23349f</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Cloud Infrastructure &amp; Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>PlayStation</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7bbfa5155595ec72</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Data Solutions developer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Engineering and Automation , Aerospace &amp; Defense</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1839a40f359e0a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Cloud Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Zoom Communications</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Platform Engineer (175364)</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Sr. Azure Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Lobel Financial</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Anaheim, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0db6ac7cf2f086e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Hyland</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3cb901e68315ba1</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Software Developer 2</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>BLOC Resources, LLC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f6e507178eea68</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Software Developer / Data Solutions Developer</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>4P Consulting Inc.</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Sarnova HC, LLC</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Sarnova HC, LLC</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Dublin, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Databricks Developer</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Hanover, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Oracle, ETL, ELT, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a28485007e465c63</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Software Engineer II, Fintech</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Twitch</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c724ec5809ede378</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Software Engineer II, Fintech</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Twitch</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=71ec45fe0952b39c</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Generative AI Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1b15647f88acc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Data Engineer BILH Pharmacy Westwood, Ma, Hybrid / on-site</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Beth Israel Lahey Health</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Westwood, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Data Modeling, ETL, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf255b6550fc872f</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Sr. Scientific Data Engineer, R&amp;D Data Platform</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Abbott</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Abbott Park, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, RDS, Unity Catalog, Spark</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8280545268f9a67b</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Infrastructure Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Tapestry</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Spark, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18a7770f9ee523e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Imprint</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d618dcf278adc42</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Imprint</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cae136048a3d8779</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Connected Vehicle Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Textron Specialized Vehicles</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Augusta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, ETL, MLOps, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac0a590ec45dcb</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Controller Transformation Analyst</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Newark, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>The Hartford</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer I</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Braze</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64543ec5f02890f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer I</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Braze</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15a494f407d22227</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer I</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Braze</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2546a365f20e983</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer I</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Braze</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7988a3ee97db7900</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9ca78d46c32c41</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>AI Agentic Software Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Siemens</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Senior Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Software Developer Senior</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>City of Charlotte, NC</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8009ac0fbc46342</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ff332af76c49db</t>
         </is>
       </c>
     </row>
